--- a/kahoot/orientation/history/9_finnish_history__0001.xlsx
+++ b/kahoot/orientation/history/9_finnish_history__0001.xlsx
@@ -1835,7 +1835,7 @@
       </c>
       <c r="D9" s="14" t="inlineStr">
         <is>
-          <t>En historiskt definierad social klass med särskilda rättigheter och skyldigheter</t>
+          <t>En social klass med särskilda rättigheter och skyldigheter</t>
         </is>
       </c>
       <c r="E9" s="14" t="inlineStr">
@@ -1949,7 +1949,7 @@
       </c>
       <c r="D11" s="21" t="inlineStr">
         <is>
-          <t>De tillhörde ofta inget stånd och hade inte samma rättigheter som ståndmedlemmar</t>
+          <t>De tillhörde ofta inget stånd och saknade samma rättigheter</t>
         </is>
       </c>
       <c r="E11" s="14" t="inlineStr">
@@ -2063,7 +2063,7 @@
       </c>
       <c r="D13" s="14" t="inlineStr">
         <is>
-          <t>Finland kunde bestämma mycket internt men var fortfarande en del av Ryssland</t>
+          <t>Finland styrde mycket internt men var del av Ryssland</t>
         </is>
       </c>
       <c r="E13" s="14" t="inlineStr">
@@ -2234,7 +2234,7 @@
       </c>
       <c r="D16" s="14" t="inlineStr">
         <is>
-          <t>En stat som garanterar alla en grundinkomst och en miniminivå för levnadsstandard</t>
+          <t>En stat som garanterar grundtrygghet och miniminivå i levnadsstandard</t>
         </is>
       </c>
       <c r="E16" s="14" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="D17" s="14" t="inlineStr">
         <is>
-          <t>En period av ekonomisk nedgång med ökande arbetslöshet och svårigheter för företag</t>
+          <t>En period av ekonomisk nedgång med ökande arbetslöshet</t>
         </is>
       </c>
       <c r="E17" s="14" t="inlineStr">
@@ -2348,7 +2348,7 @@
       </c>
       <c r="D18" s="14" t="inlineStr">
         <is>
-          <t>Befolkningens åldersstruktur och relationen mellan personer i arbetsför ålder och försörjda</t>
+          <t>Förhållandet mellan arbetsföra och försörjda i befolkningen</t>
         </is>
       </c>
       <c r="E18" s="14" t="inlineStr">
